--- a/exports/ONGC_full_report.xlsx
+++ b/exports/ONGC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44614.55208333334</v>
+        <v>44615.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>148.7</v>
+        <v>146.05</v>
       </c>
       <c r="I2" t="n">
         <v>146.5732155575265</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>5.05</v>
+        <v>3.18</v>
       </c>
       <c r="L2" t="n">
         <v>0.11</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44623.38541666666</v>
+        <v>44623.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>149.1</v>
+        <v>153.95</v>
       </c>
       <c r="I3" t="n">
         <v>151.8109791874822</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.09</v>
+        <v>-5.41</v>
       </c>
       <c r="L3" t="n">
-        <v>4.18</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
         <v>3.31</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>155.05</v>
+        <v>146.5</v>
       </c>
       <c r="I4" t="n">
         <v>149.1176988984275</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>0.71</v>
+        <v>-4.84</v>
       </c>
       <c r="L4" t="n">
-        <v>3.73</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>3.67</v>
       </c>
       <c r="N4" t="n">
-        <v>4.24</v>
+        <v>4.74</v>
       </c>
       <c r="O4" t="n">
         <v>4.51</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.04</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>157.25</v>
+        <v>159.05</v>
       </c>
       <c r="I5" t="n">
         <v>157.4893486522944</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.34</v>
+        <v>-8.57</v>
       </c>
       <c r="L5" t="n">
         <v>11.77</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>4.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>157.35</v>
+        <v>152.75</v>
       </c>
       <c r="I6" t="n">
         <v>152.7895101489378</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.07</v>
+        <v>-3.96</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>4.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>1.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0.76</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.02</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.79</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44687.38541666666</v>
+        <v>44687.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>148</v>
+        <v>150.65</v>
       </c>
       <c r="I7" t="n">
         <v>150.2290603972248</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3.11</v>
+        <v>1.37</v>
       </c>
       <c r="L7" t="n">
         <v>2.32</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>143.25</v>
+        <v>138.45</v>
       </c>
       <c r="I8" t="n">
         <v>140.0129876884384</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.91</v>
+        <v>-8.1</v>
       </c>
       <c r="L8" t="n">
-        <v>5.91</v>
+        <v>8.26</v>
       </c>
       <c r="M8" t="n">
         <v>2.62</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>139.1</v>
+        <v>147.05</v>
       </c>
       <c r="I9" t="n">
         <v>142.5533661495851</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.47</v>
+        <v>-6.21</v>
       </c>
       <c r="L9" t="n">
         <v>7.33</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>10.2</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44726.55208333334</v>
+        <v>44727.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>140.95</v>
+        <v>139</v>
       </c>
       <c r="I10" t="n">
         <v>139.7836720333874</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.15</v>
+        <v>-5.47</v>
       </c>
       <c r="L10" t="n">
-        <v>5.24</v>
+        <v>5.78</v>
       </c>
       <c r="M10" t="n">
         <v>1.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="O10" t="n">
         <v>4.85</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>128.3</v>
+        <v>132.7</v>
       </c>
       <c r="I11" t="n">
         <v>132.2325028483974</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>7.7</v>
+        <v>4.53</v>
       </c>
       <c r="L11" t="n">
         <v>2.23</v>
@@ -1068,7 +1199,7 @@
         <v>2.22</v>
       </c>
       <c r="N11" t="n">
-        <v>3.63</v>
+        <v>4.95</v>
       </c>
       <c r="O11" t="n">
         <v>-3.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44742.55208333334</v>
+        <v>44743.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>136.4</v>
+        <v>119</v>
       </c>
       <c r="I12" t="n">
         <v>124.4589145747687</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.79</v>
+        <v>-10.32</v>
       </c>
       <c r="L12" t="n">
-        <v>2.83</v>
+        <v>11.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0.47</v>
+        <v>1.32</v>
       </c>
       <c r="N12" t="n">
-        <v>1.84</v>
+        <v>12.94</v>
       </c>
       <c r="O12" t="n">
         <v>4.95</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>21.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44771.38541666666</v>
+        <v>44771.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>120.45</v>
+        <v>121.3</v>
       </c>
       <c r="I13" t="n">
         <v>120.577261491193</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.22</v>
+        <v>-1.93</v>
       </c>
       <c r="L13" t="n">
         <v>14.71</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.87</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>121.5</v>
+        <v>119.3</v>
       </c>
       <c r="I14" t="n">
         <v>119.3684993317838</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>0.16</v>
+        <v>-1.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.57</v>
+        <v>3.22</v>
       </c>
       <c r="M14" t="n">
         <v>1.15</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.62</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44833.55208333334</v>
+        <v>44834.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>114.75</v>
+        <v>117.75</v>
       </c>
       <c r="I15" t="n">
         <v>116.7885522227271</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>3.81</v>
+        <v>1.3</v>
       </c>
       <c r="L15" t="n">
         <v>5.95</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.79</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>128.5</v>
+        <v>122.05</v>
       </c>
       <c r="I16" t="n">
         <v>124.8373155513718</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K16" t="n">
-        <v>9.130000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>3.65</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>4.36</v>
       </c>
       <c r="N16" t="n">
-        <v>1.79</v>
+        <v>4.59</v>
       </c>
       <c r="O16" t="n">
         <v>-0.13</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.77</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44897.55208333334</v>
+        <v>44900.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>127.2</v>
+        <v>128.95</v>
       </c>
       <c r="I17" t="n">
         <v>127.8048562900705</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.22</v>
+        <v>-5.65</v>
       </c>
       <c r="L17" t="n">
         <v>7.21</v>
@@ -1410,7 +1613,7 @@
         <v>1.34</v>
       </c>
       <c r="N17" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
         <v>-4.59</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>4.81</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>128.55</v>
+        <v>126.85</v>
       </c>
       <c r="I18" t="n">
         <v>128.5373233241655</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.31</v>
+        <v>-1.63</v>
       </c>
       <c r="L18" t="n">
         <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="N18" t="n">
         <v>1.67</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.19</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>131.1</v>
+        <v>133.15</v>
       </c>
       <c r="I19" t="n">
         <v>133.0137103845078</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.35</v>
+        <v>-4.97</v>
       </c>
       <c r="L19" t="n">
-        <v>4.02</v>
+        <v>6.03</v>
       </c>
       <c r="M19" t="n">
         <v>0.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.45</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>138.4</v>
+        <v>133.25</v>
       </c>
       <c r="I20" t="n">
         <v>133.6192504439083</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>3.94</v>
+        <v>0.08</v>
       </c>
       <c r="L20" t="n">
         <v>2.14</v>
@@ -1581,7 +1820,7 @@
         <v>0.78</v>
       </c>
       <c r="N20" t="n">
-        <v>2.07</v>
+        <v>3.58</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.36</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>133.3</v>
+        <v>138.75</v>
       </c>
       <c r="I21" t="n">
         <v>134.8101262928076</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04</v>
+        <v>-4.13</v>
       </c>
       <c r="L21" t="n">
         <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0.64</v>
+        <v>1.69</v>
       </c>
       <c r="N21" t="n">
-        <v>1.58</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
         <v>-3.58</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.82</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45006.38541666666</v>
+        <v>45006.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>137</v>
+        <v>136.55</v>
       </c>
       <c r="I22" t="n">
         <v>136.8344059357648</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.26</v>
+        <v>-1.59</v>
       </c>
       <c r="L22" t="n">
         <v>3.6</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>4.58</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>136.5</v>
+        <v>139.15</v>
       </c>
       <c r="I23" t="n">
         <v>138.9129452097463</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.04</v>
+        <v>-1.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>4.43</v>
       </c>
       <c r="M23" t="n">
-        <v>0.84</v>
+        <v>2.27</v>
       </c>
       <c r="N23" t="n">
         <v>2.25</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>4.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>148.25</v>
+        <v>144</v>
       </c>
       <c r="I24" t="n">
         <v>146.7222003762636</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>6.54</v>
+        <v>3.49</v>
       </c>
       <c r="L24" t="n">
         <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="N24" t="n">
-        <v>2.02</v>
+        <v>3.04</v>
       </c>
       <c r="O24" t="n">
         <v>1.83</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>3.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45098.38541666666</v>
+        <v>45098.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>143.2</v>
+        <v>144.8</v>
       </c>
       <c r="I25" t="n">
         <v>144.0969508885431</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>3.45</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45198.55208333334</v>
+        <v>45202.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>173.3</v>
+        <v>166.8</v>
       </c>
       <c r="I26" t="n">
         <v>167.022199070441</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>100</v>
+        <v>103.8333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>19.68</v>
+        <v>15.19</v>
       </c>
       <c r="L26" t="n">
         <v>2.94</v>
       </c>
       <c r="M26" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="O26" t="n">
         <v>1.83</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.46</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>168</v>
+        <v>170.55</v>
       </c>
       <c r="I27" t="n">
         <v>168.7116350051175</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.72</v>
+        <v>-2.25</v>
       </c>
       <c r="L27" t="n">
         <v>2.55</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.11</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45272.55208333334</v>
+        <v>45273.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>182.5</v>
+        <v>179.95</v>
       </c>
       <c r="I28" t="n">
         <v>180.0899786505607</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>7.01</v>
+        <v>5.51</v>
       </c>
       <c r="L28" t="n">
         <v>2.4</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.88</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45279.55208333334</v>
+        <v>45280.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>186.6</v>
+        <v>193.3</v>
       </c>
       <c r="I29" t="n">
         <v>189.3219067568619</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.7</v>
+        <v>-7.42</v>
       </c>
       <c r="L29" t="n">
-        <v>5.31</v>
+        <v>9.67</v>
       </c>
       <c r="M29" t="n">
         <v>1.39</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>251.4</v>
+        <v>242.25</v>
       </c>
       <c r="I30" t="n">
         <v>249.6156485478764</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K30" t="n">
-        <v>30.06</v>
+        <v>25.32</v>
       </c>
       <c r="L30" t="n">
         <v>3.23</v>
@@ -2151,7 +2510,7 @@
         <v>2.3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.57</v>
+        <v>5.19</v>
       </c>
       <c r="O30" t="n">
         <v>1.96</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>8.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>253.75</v>
+        <v>257.15</v>
       </c>
       <c r="I31" t="n">
         <v>256.6671154995516</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.75</v>
+        <v>-6.15</v>
       </c>
       <c r="L31" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="M31" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="N31" t="n">
         <v>3.08</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.78</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>262.65</v>
+        <v>255.6</v>
       </c>
       <c r="I32" t="n">
         <v>256.1009505733938</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>2.14</v>
+        <v>-0.6</v>
       </c>
       <c r="L32" t="n">
         <v>4.08</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.16</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>247.3</v>
+        <v>264.45</v>
       </c>
       <c r="I33" t="n">
         <v>259.9527288318039</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>-3.46</v>
       </c>
       <c r="L33" t="n">
         <v>4.13</v>
       </c>
       <c r="M33" t="n">
-        <v>1.48</v>
+        <v>4.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.63</v>
+        <v>6.85</v>
       </c>
       <c r="O33" t="n">
         <v>-3.08</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.18</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>264.25</v>
+        <v>224.5</v>
       </c>
       <c r="I34" t="n">
         <v>248.3219856816149</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.08</v>
+        <v>-15.11</v>
       </c>
       <c r="L34" t="n">
-        <v>3.86</v>
+        <v>21.52</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>16.16</v>
       </c>
       <c r="O34" t="n">
         <v>6.85</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>19.59</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>254.95</v>
+        <v>258</v>
       </c>
       <c r="I35" t="n">
         <v>257.4228224381027</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.56</v>
+        <v>-14.92</v>
       </c>
       <c r="L35" t="n">
         <v>18.17</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>299.05</v>
+        <v>286.25</v>
       </c>
       <c r="I36" t="n">
         <v>289.4125189931392</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>15.91</v>
+        <v>10.95</v>
       </c>
       <c r="L36" t="n">
         <v>4.92</v>
       </c>
       <c r="M36" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="N36" t="n">
         <v>3.71</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>8.98</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>311.7</v>
+        <v>315.35</v>
       </c>
       <c r="I37" t="n">
         <v>311.9629789097412</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.890000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="L37" t="n">
-        <v>10.39</v>
+        <v>12.09</v>
       </c>
       <c r="M37" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="N37" t="n">
         <v>4.11</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.11</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>307.5</v>
+        <v>289.6</v>
       </c>
       <c r="I38" t="n">
         <v>296.0832886480358</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.49</v>
+        <v>-8.17</v>
       </c>
       <c r="L38" t="n">
-        <v>2.98</v>
+        <v>9.69</v>
       </c>
       <c r="M38" t="n">
-        <v>0.88</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>3.12</v>
+        <v>6.03</v>
       </c>
       <c r="O38" t="n">
         <v>1.83</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.19</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45516.38541666666</v>
+        <v>45516.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>307.5</v>
+        <v>317.45</v>
       </c>
       <c r="I39" t="n">
         <v>313.1863056678393</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.18</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>7.94</v>
+        <v>10.79</v>
       </c>
       <c r="M39" t="n">
         <v>3.14</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>299.6</v>
+        <v>291.7</v>
       </c>
       <c r="I40" t="n">
         <v>295.0886312893273</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.62</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>6.88</v>
+        <v>9.58</v>
       </c>
       <c r="M40" t="n">
-        <v>0.26</v>
+        <v>2.14</v>
       </c>
       <c r="N40" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>234.25</v>
+        <v>246.4</v>
       </c>
       <c r="I41" t="n">
         <v>244.1114573722292</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K41" t="n">
-        <v>19.69</v>
+        <v>15.53</v>
       </c>
       <c r="L41" t="n">
         <v>1.13</v>
@@ -2778,7 +3269,7 @@
         <v>2.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>5.23</v>
       </c>
       <c r="O41" t="n">
         <v>-2.17</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.87</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>238.15</v>
+        <v>235.55</v>
       </c>
       <c r="I42" t="n">
         <v>238.1440315173165</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.35</v>
+        <v>-4.4</v>
       </c>
       <c r="L42" t="n">
-        <v>4.04</v>
+        <v>4.61</v>
       </c>
       <c r="M42" t="n">
         <v>0.59</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.53</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>225.95</v>
+        <v>233.55</v>
       </c>
       <c r="I43" t="n">
         <v>232.2087580655038</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>4.08</v>
+        <v>0.85</v>
       </c>
       <c r="L43" t="n">
         <v>1.15</v>
@@ -2892,7 +3407,7 @@
         <v>0.33</v>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>3.87</v>
       </c>
       <c r="O43" t="n">
         <v>-1.92</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.15</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>246.25</v>
+        <v>241.5</v>
       </c>
       <c r="I44" t="n">
         <v>243.9965480089948</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K44" t="n">
-        <v>5.44</v>
+        <v>3.4</v>
       </c>
       <c r="L44" t="n">
         <v>3.21</v>
       </c>
       <c r="M44" t="n">
-        <v>0.38</v>
+        <v>1.24</v>
       </c>
       <c r="N44" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
         <v>3.87</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.25</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>247.9</v>
+        <v>250.6</v>
       </c>
       <c r="I45" t="n">
         <v>250.0490471297998</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.65</v>
+        <v>-3.77</v>
       </c>
       <c r="L45" t="n">
-        <v>2.84</v>
+        <v>4.06</v>
       </c>
       <c r="M45" t="n">
         <v>0.04</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>245.75</v>
+        <v>234.7</v>
       </c>
       <c r="I46" t="n">
         <v>236.1405376603245</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.94</v>
+        <v>-6.34</v>
       </c>
       <c r="L46" t="n">
-        <v>3.43</v>
+        <v>6.82</v>
       </c>
       <c r="M46" t="n">
         <v>1.22</v>
       </c>
       <c r="N46" t="n">
-        <v>1.94</v>
+        <v>2.58</v>
       </c>
       <c r="O46" t="n">
         <v>2.24</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>222.05</v>
+        <v>224.65</v>
       </c>
       <c r="I47" t="n">
         <v>224.2967539837651</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K47" t="n">
-        <v>5.39</v>
+        <v>4.28</v>
       </c>
       <c r="L47" t="n">
         <v>6.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.33</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>232.3</v>
+        <v>215.9</v>
       </c>
       <c r="I48" t="n">
         <v>224.826203385592</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>3.41</v>
+        <v>-3.89</v>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>4.12</v>
       </c>
       <c r="M48" t="n">
-        <v>0.42</v>
+        <v>1.25</v>
       </c>
       <c r="N48" t="n">
-        <v>1.92</v>
+        <v>7.17</v>
       </c>
       <c r="O48" t="n">
         <v>1.22</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.79</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>219.55</v>
+        <v>222.4</v>
       </c>
       <c r="I49" t="n">
         <v>222.3270171717116</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.69</v>
+        <v>-3.01</v>
       </c>
       <c r="L49" t="n">
         <v>6.55</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.84</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>227.6</v>
+        <v>226.05</v>
       </c>
       <c r="I50" t="n">
         <v>227.1922630343485</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="L50" t="n">
         <v>1.33</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45791.38541666666</v>
+        <v>45791.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>234.1</v>
+        <v>234.65</v>
       </c>
       <c r="I51" t="n">
         <v>234.2677001227371</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.56</v>
+        <v>-3.8</v>
       </c>
       <c r="L51" t="n">
         <v>4.16</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>228.1</v>
+        <v>227.25</v>
       </c>
       <c r="I52" t="n">
         <v>227.6263295344951</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.79</v>
+        <v>-3.15</v>
       </c>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>3.41</v>
       </c>
       <c r="M52" t="n">
         <v>0.5600000000000001</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.07</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>233.6</v>
+        <v>237.35</v>
       </c>
       <c r="I53" t="n">
         <v>233.8031960743889</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.79</v>
+        <v>-4.44</v>
       </c>
       <c r="L53" t="n">
-        <v>2.82</v>
+        <v>5.08</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45832.38541666666</v>
+        <v>45832.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>233.3</v>
+        <v>232.75</v>
       </c>
       <c r="I54" t="n">
         <v>233.1058639842337</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.71</v>
+        <v>-1.94</v>
       </c>
       <c r="L54" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
         <v>1.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.44</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45901.38541666666</v>
+        <v>45901.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>224.85</v>
+        <v>227.9</v>
       </c>
       <c r="I55" t="n">
         <v>227.8580520833819</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>68.83333333333333</v>
+        <v>69</v>
       </c>
       <c r="K55" t="n">
-        <v>3.39</v>
+        <v>2.08</v>
       </c>
       <c r="L55" t="n">
         <v>1.35</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>3.72</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>221.95</v>
+        <v>220.65</v>
       </c>
       <c r="I56" t="n">
         <v>221.3908628252838</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.61</v>
+        <v>-3.18</v>
       </c>
       <c r="L56" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="M56" t="n">
         <v>0.2</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>4.01</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>225.9</v>
+        <v>228</v>
       </c>
       <c r="I57" t="n">
         <v>227.1336933570227</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.38</v>
+        <v>-3.33</v>
       </c>
       <c r="L57" t="n">
-        <v>3.06</v>
+        <v>3.72</v>
       </c>
       <c r="M57" t="n">
         <v>0.52</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>3.17</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>239.85</v>
+        <v>235.55</v>
       </c>
       <c r="I58" t="n">
         <v>236.7427078656574</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2</v>
+        <v>3.31</v>
       </c>
       <c r="L58" t="n">
         <v>1.18</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.63</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46022.38541666666</v>
+        <v>46022.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>233.1</v>
+        <v>234.95</v>
       </c>
       <c r="I59" t="n">
         <v>233.9521344335425</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
       <c r="L59" t="n">
         <v>4.16</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.45</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>233.7</v>
+        <v>226.2</v>
       </c>
       <c r="I60" t="n">
         <v>228.450212504014</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.53</v>
+        <v>-3.72</v>
       </c>
       <c r="L60" t="n">
-        <v>1.98</v>
+        <v>3.79</v>
       </c>
       <c r="M60" t="n">
         <v>0.66</v>
       </c>
       <c r="N60" t="n">
-        <v>1.63</v>
+        <v>3.34</v>
       </c>
       <c r="O60" t="n">
         <v>2.55</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.97</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>230.15</v>
+        <v>236.7</v>
       </c>
       <c r="I61" t="n">
         <v>235.75967682099</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.75</v>
+        <v>-4.64</v>
       </c>
       <c r="L61" t="n">
-        <v>3.18</v>
+        <v>5.08</v>
       </c>
       <c r="M61" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="N61" t="n">
-        <v>1.2</v>
+        <v>3.37</v>
       </c>
       <c r="O61" t="n">
         <v>-3.34</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.66</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>254.55</v>
+        <v>248.65</v>
       </c>
       <c r="I62" t="n">
         <v>254.2455598392193</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>7.54</v>
+        <v>5.05</v>
       </c>
       <c r="L62" t="n">
         <v>2.66</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46064.38541666666</v>
+        <v>46064.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>262.25</v>
+        <v>268.35</v>
       </c>
       <c r="I63" t="n">
         <v>266.6941857084855</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.47</v>
+        <v>-7.92</v>
       </c>
       <c r="L63" t="n">
-        <v>7.28</v>
+        <v>8.1</v>
       </c>
       <c r="M63" t="n">
         <v>2.11</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.22</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46093.55208333334</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>270.6</v>
+        <v>264.2</v>
       </c>
       <c r="I64" t="n">
         <v>268.5295601149671</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>0.84</v>
+        <v>-1.55</v>
       </c>
       <c r="L64" t="n">
         <v>3.28</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.88</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46106.55208333334</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>269.7</v>
+        <v>282.8</v>
       </c>
       <c r="I65" t="n">
         <v>276.6374734144949</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.08</v>
+        <v>-7.04</v>
       </c>
       <c r="L65" t="n">
-        <v>3.44</v>
+        <v>7.19</v>
       </c>
       <c r="M65" t="n">
         <v>1.19</v>
       </c>
       <c r="N65" t="n">
-        <v>1.92</v>
+        <v>4.23</v>
       </c>
       <c r="O65" t="n">
         <v>-2.37</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46146.55208333334</v>
+        <v>46147.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>292.9</v>
+        <v>289.3</v>
       </c>
       <c r="I66" t="n">
         <v>290.1315584431</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K66" t="n">
-        <v>3.57</v>
+        <v>2.3</v>
       </c>
       <c r="L66" t="n">
         <v>4.63</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.05</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>280.45</v>
+        <v>295.25</v>
       </c>
       <c r="I67" t="n">
         <v>292.6477651178848</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>3.06</v>
+        <v>-2.06</v>
       </c>
       <c r="L67" t="n">
-        <v>2.28</v>
+        <v>3.66</v>
       </c>
       <c r="M67" t="n">
-        <v>0.54</v>
+        <v>2.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0.96</v>
+        <v>4.9</v>
       </c>
       <c r="O67" t="n">
         <v>-0.87</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.45</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>290</v>
+        <v>284.9</v>
       </c>
       <c r="I68" t="n">
         <v>286.0894704394688</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.78</v>
+        <v>-3.51</v>
       </c>
       <c r="L68" t="n">
-        <v>2.85</v>
+        <v>3.71</v>
       </c>
       <c r="M68" t="n">
         <v>0.82</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.5</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>242.19</v>
+        <v>247</v>
       </c>
       <c r="I69" t="n">
         <v>243.8270028036224</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K69" t="n">
-        <v>14.99</v>
+        <v>13.3</v>
       </c>
       <c r="L69" t="n">
         <v>1.77</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.73</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>249</v>
+        <v>241.11</v>
       </c>
       <c r="I70" t="n">
         <v>245.1383076687957</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8100000000000001</v>
+        <v>-2.38</v>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="M70" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="N70" t="n">
-        <v>1.42</v>
+        <v>4.26</v>
       </c>
       <c r="O70" t="n">
         <v>1.45</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.29</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46318.55208333334</v>
+        <v>46321.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>225.7</v>
+        <v>227.38</v>
       </c>
       <c r="I71" t="n">
         <v>227.2121244194838</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K71" t="n">
-        <v>6.39</v>
+        <v>5.69</v>
       </c>
       <c r="L71" t="n">
         <v>2.93</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,12 @@
       <c r="Q72" t="n">
         <v>4</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6650,7 +7519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -6660,7 +7529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.6</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7">
@@ -6670,7 +7539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="8">
@@ -6680,7 +7549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6690,7 +7559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="10">
@@ -6700,7 +7569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.2</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="11">
@@ -6710,7 +7579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -6720,7 +7589,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6730,7 +7599,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6740,7 +7609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.36</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="15">
@@ -6750,7 +7619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.79</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="16">
@@ -6760,7 +7629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6770,7 +7639,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.06</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="18">
@@ -6780,7 +7649,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.6</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="19">
@@ -6790,7 +7659,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.03</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="20">
@@ -6800,7 +7669,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.2</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="21">
@@ -6810,7 +7679,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.17</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="22">
@@ -6820,7 +7689,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6830,7 +7699,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6840,7 +7709,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="25">
@@ -6860,7 +7729,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.72</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="27">
@@ -6870,7 +7739,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.06</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="28">
@@ -6880,7 +7749,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
